--- a/patient_feedback_forms/029_rare_disease_patient_feedback--patient_feedback_forms.xlsx
+++ b/patient_feedback_forms/029_rare_disease_patient_feedback--patient_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pain'}</t>
+          <t>pain</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pain'}</t>
+          <t>Pain</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'nausea'}</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Nausea'}</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'side_effects'}</t>
+          <t>side_effects</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Side effects'}</t>
+          <t>Side effects</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cost'}</t>
+          <t>Cost</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'access'}</t>
+          <t>access</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Access'}</t>
+          <t>Access</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Somewhat good'}</t>
+          <t>Somewhat good</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_very_good'}</t>
+          <t>not_very_good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not very good'}</t>
+          <t>Not very good</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'not_good_at_all'}</t>
+          <t>not_good_at_all</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Not good at all'}</t>
+          <t>Not good at all</t>
         </is>
       </c>
     </row>
